--- a/astro-site/public/dl/kit-tareas-hotel/15-spa-wellness.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/15-spa-wellness.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Verificar temperatura de piscina/jacuzzi (35-38 °C) y ajustar</t>
+          <t>Verificar temperatura del jacuzzi (35-38 °C) y ajustar</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Apagar saunas, baño de vapor y jacuzzi</t>
+          <t>Apagar saunas y baño de vapor; en el jacuzzi apagar solo chorros y soplante: la filtración, la recirculación y la desinfección siguen en marcha toda la noche</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
